--- a/Тест2/279.xlsx
+++ b/Тест2/279.xlsx
@@ -126,19 +126,19 @@
     <t xml:space="preserve">Go'shtga Proteus qanday yo'llar bilan tushishi mumkin?</t>
   </si>
   <si>
-    <t xml:space="preserve">Quyosh nuri va yomg'ir tomchilari orqali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elektr toki va tovush to'lqinlari orqali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magnit maydoni va nur orqali</t>
+    <t xml:space="preserve">Quyosh nuri va yomg'ir tomchilari orqali tushadi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elektr toki va tovush to'lqinlari orqali tushadi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnit maydoni va yorug'lik nurlari orqali tushadi</t>
   </si>
   <si>
     <t xml:space="preserve">Ichak tarkibi, tuproq, suv yoki xodim qo'li orqali</t>
   </si>
   <si>
-    <t xml:space="preserve">Radio to'lqinlar va shamol orqali</t>
+    <t xml:space="preserve">Radio to'lqinlar va shamol oqimi orqali tushadi</t>
   </si>
   <si>
     <t xml:space="preserve">To'g'ri javob: Ichak tarkibi, tuproq, suv yoki xodim qo'li orqali. Go'shtga Proteus ichak tarkibi, tuproq, suv yoki xodimning qo'llari orqali tushishi mumkin. Manba: Mavzu materiali (279.docx).</t>
